--- a/outputs/portfolio-content-editor/Portfolio-Content-Editor.xlsx
+++ b/outputs/portfolio-content-editor/Portfolio-Content-Editor.xlsx
@@ -42,7 +42,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Project Screens'!$A$1:$D$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Project Images'!$A$1:$D$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Badges'!$A$1:$D$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Certificates'!$A$1:$D$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Certificates'!$A$1:$E$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Settings'!$A$1:$B$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -284,13 +284,14 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="TCertificates" displayName="TCertificates" ref="A1:D10" headerRowCount="1">
-  <autoFilter ref="A1:D10"/>
-  <tableColumns count="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="TCertificates" displayName="TCertificates" ref="A1:E10" headerRowCount="1">
+  <autoFilter ref="A1:E10"/>
+  <tableColumns count="5">
     <tableColumn id="1" name="Name"/>
     <tableColumn id="2" name="Short name"/>
     <tableColumn id="3" name="Verification URL"/>
     <tableColumn id="4" name="Provider"/>
+    <tableColumn id="5" name="Image path"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -715,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -827,6 +828,18 @@
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>This workbook is the convenient editing copy. The website consumes the JSON files generated by the sync script.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Certificate images</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Put images in assets/images/certificates/. Enter their paths under Certificates &gt; Image path, then sync the workbook.</t>
         </is>
       </c>
     </row>
@@ -4375,13 +4388,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="90" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -4405,6 +4422,11 @@
           <t>Provider</t>
         </is>
       </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Image path</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
@@ -4427,6 +4449,11 @@
           <t>HackerRank skill certificate</t>
         </is>
       </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>../assets/images/certificates/python-basic.svg</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
@@ -4449,6 +4476,11 @@
           <t>HackerRank skill certificate</t>
         </is>
       </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>../assets/images/certificates/problem-solving-basic.png</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -4471,6 +4503,11 @@
           <t>HackerRank skill certificate</t>
         </is>
       </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>../assets/images/certificates/sql-basic.png</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -4493,6 +4530,11 @@
           <t>HackerRank skill certificate</t>
         </is>
       </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>../assets/images/certificates/sql-intermediate.png</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -4515,6 +4557,11 @@
           <t>HackerRank skill certificate</t>
         </is>
       </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>../assets/images/certificates/javascript-basic.png</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -4537,6 +4584,11 @@
           <t>HackerRank skill certificate</t>
         </is>
       </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>../assets/images/certificates/sql-advanced.png</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -4559,6 +4611,11 @@
           <t>HackerRank skill certificate</t>
         </is>
       </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>../assets/images/certificates/problem-solving-intermediate.png</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -4581,6 +4638,11 @@
           <t>HackerRank skill certificate</t>
         </is>
       </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>../assets/images/certificates/java-basic.png</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -4603,9 +4665,14 @@
           <t>HackerRank skill certificate</t>
         </is>
       </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>../assets/images/certificates/react-basic.png</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D10"/>
+  <autoFilter ref="A1:E10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/outputs/portfolio-content-editor/Portfolio-Content-Editor.xlsx
+++ b/outputs/portfolio-content-editor/Portfolio-Content-Editor.xlsx
@@ -5479,7 +5479,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Open to junior Java backend and backend developer roles</t>
+          <t>Open to Java backend developer roles</t>
         </is>
       </c>
     </row>

--- a/outputs/portfolio-content-editor/Portfolio-Content-Editor.xlsx
+++ b/outputs/portfolio-content-editor/Portfolio-Content-Editor.xlsx
@@ -4478,7 +4478,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>../assets/images/certificates/problem-solving-basic.png</t>
+          <t>../assets/images/certificates/problem-solving-basic.svg</t>
         </is>
       </c>
     </row>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>../assets/images/certificates/sql-basic.png</t>
+          <t>../assets/images/certificates/sql-basic.svg</t>
         </is>
       </c>
     </row>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>../assets/images/certificates/sql-intermediate.png</t>
+          <t>../assets/images/certificates/sql-intermediate.svg</t>
         </is>
       </c>
     </row>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>../assets/images/certificates/javascript-basic.png</t>
+          <t>../assets/images/certificates/javascript-basic.svg</t>
         </is>
       </c>
     </row>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>../assets/images/certificates/sql-advanced.png</t>
+          <t>../assets/images/certificates/sql-advanced.svg</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>../assets/images/certificates/problem-solving-intermediate.png</t>
+          <t>../assets/images/certificates/problem-solving-intermediate.svg</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>../assets/images/certificates/java-basic.png</t>
+          <t>../assets/images/certificates/java-basic.svg</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>../assets/images/certificates/react-basic.png</t>
+          <t>../assets/images/certificates/react-basic.svg</t>
         </is>
       </c>
     </row>

--- a/outputs/portfolio-content-editor/Portfolio-Content-Editor.xlsx
+++ b/outputs/portfolio-content-editor/Portfolio-Content-Editor.xlsx
@@ -1031,6 +1031,16 @@
 JUnit</t>
         </is>
       </c>
+      <c r="P2" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/repo/commerce-core</t>
+        </is>
+      </c>
+      <c r="Q2" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/demo/commerce-core</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
@@ -1096,6 +1106,16 @@
 JUnit</t>
         </is>
       </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/repo/event-flow</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/demo/event-flow</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -1161,6 +1181,16 @@
 JUnit</t>
         </is>
       </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/repo/stockroom</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/demo/stockroom</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -1226,6 +1256,16 @@
 AWS RDS</t>
         </is>
       </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/repo/shipshape</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/demo/shipshape</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -1291,6 +1331,16 @@
 Docker</t>
         </is>
       </c>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/repo/quickcache</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/demo/quickcache</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -1356,6 +1406,16 @@
 JUnit</t>
         </is>
       </c>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/repo/securegate</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/demo/securegate</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -1423,6 +1483,16 @@
       <c r="O8" s="4" t="inlineStr">
         <is>
           <t>Back-End Web Development</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/repo/tvamev-sahayak</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/demo/tvamev-sahayak</t>
         </is>
       </c>
     </row>
@@ -1496,6 +1566,16 @@
           <t>Python</t>
         </is>
       </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/repo/youtube-playlist-downloader</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/demo/youtube-playlist-downloader</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -1567,6 +1647,16 @@
           <t>Python</t>
         </is>
       </c>
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/repo/awareness-of-waste-recycling</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/demo/awareness-of-waste-recycling</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -1636,6 +1726,16 @@
       <c r="O11" s="4" t="inlineStr">
         <is>
           <t>Python</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/repo/automatic-files-distributing-application</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com/demo/automatic-files-distributing-application</t>
         </is>
       </c>
     </row>
